--- a/data/trans_bre/P1_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,75</t>
+          <t>2,73; 8,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,37</t>
+          <t>2,77; 8,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,44</t>
+          <t>-0,16; 7,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,39</t>
+          <t>3,38; 12,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,19; 92,8</t>
+          <t>24,18; 97,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,46; 88,46</t>
+          <t>22,53; 93,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 48,83</t>
+          <t>-1,5; 48,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,47; 50,16</t>
+          <t>11,22; 52,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,13</t>
+          <t>-2,97; 0,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,08</t>
+          <t>-2,98; 0,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,97</t>
+          <t>-1,95; 1,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 0,9</t>
+          <t>-7,72; 0,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 4,59</t>
+          <t>-47,62; 4,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 2,3</t>
+          <t>-43,27; 1,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 22,69</t>
+          <t>-18,24; 20,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,19; -2,26</t>
+          <t>-47,67; -0,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,46</t>
+          <t>-4,37; 2,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 3,49</t>
+          <t>-5,4; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -0,86</t>
+          <t>-9,3; -0,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,64</t>
+          <t>-3,44; 4,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 35,11</t>
+          <t>-41,26; 38,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 37,73</t>
+          <t>-37,95; 31,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,87; -3,5</t>
+          <t>-46,04; -1,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 28,46</t>
+          <t>-20,3; 36,03</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,76</t>
+          <t>0,03; 2,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,92</t>
+          <t>0,17; 2,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,08</t>
+          <t>-1,07; 2,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,55</t>
+          <t>-3,32; 3,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 42,4</t>
+          <t>0,63; 42,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 38,48</t>
+          <t>1,5; 38,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 17,62</t>
+          <t>-7,82; 20,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 24,3</t>
+          <t>-18,64; 23,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,02</t>
+          <t>2,52; 7,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,41</t>
+          <t>2,84; 8,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 7,3</t>
+          <t>-0,08; 7,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,58</t>
+          <t>2,18; 11,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,18; 97,11</t>
+          <t>20,88; 89,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,53; 93,26</t>
+          <t>22,6; 92,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 48,26</t>
+          <t>-0,36; 48,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 52,26</t>
+          <t>6,87; 43,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-29,73%</t>
+          <t>-28,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,24</t>
+          <t>-2,8; 0,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,08</t>
+          <t>-2,94; 0,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,78</t>
+          <t>-1,94; 1,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 0,49</t>
+          <t>-7,13; -2,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,62; 4,94</t>
+          <t>-45,7; 7,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 1,38</t>
+          <t>-42,79; 6,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 20,05</t>
+          <t>-18,11; 22,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,67; -0,9</t>
+          <t>-38,21; -17,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>-3,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,58</t>
+          <t>-4,8; 2,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 3,35</t>
+          <t>-5,24; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -0,28</t>
+          <t>-9,47; -0,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 4,43</t>
+          <t>-4,18; 2,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 38,39</t>
+          <t>-45,74; 32,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 31,7</t>
+          <t>-36,06; 40,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,04; -1,92</t>
+          <t>-46,1; -2,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 36,03</t>
+          <t>-23,73; 22,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,61%</t>
+          <t>-4,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,73</t>
+          <t>0,07; 2,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,95</t>
+          <t>0,14; 3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,47</t>
+          <t>-1,11; 2,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,44</t>
+          <t>-2,43; 0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 42,5</t>
+          <t>0,89; 44,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 38,16</t>
+          <t>1,5; 41,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 20,63</t>
+          <t>-8,23; 18,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 23,3</t>
+          <t>-12,71; 5,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
